--- a/Honda_Logi/Excel_Format/モジュール別包装費明細.xlsx
+++ b/Honda_Logi/Excel_Format/モジュール別包装費明細.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01_hida_data\78_Honda_ロジ\01_PG\git\Honda_Logi\Excel_Format\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{452B2383-D1B6-4C15-B6B2-20CC881310A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8338A95D-AB61-4E97-86D2-366871959320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1965" windowWidth="25440" windowHeight="15390" xr2:uid="{8DDBEA3C-F131-4B47-9603-2E5186CE90A5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{8DDBEA3C-F131-4B47-9603-2E5186CE90A5}"/>
   </bookViews>
   <sheets>
     <sheet name="モジュール別包装費明細" sheetId="1" r:id="rId1"/>
@@ -36,45 +36,29 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
-  <si>
-    <t>■2025年09月度　モジュール別包装費明細</t>
-    <rPh sb="16" eb="17">
-      <t>ベツ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ホウソウ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>メイサイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>DIST：</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>機種：</t>
     <rPh sb="0" eb="2">
       <t>キシュ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>モジュール№：</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>モデフ：</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>カテゴリ</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>業務内容</t>
@@ -84,7 +68,7 @@
     <rPh sb="2" eb="4">
       <t>ナイヨウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>工数(秒)</t>
@@ -94,14 +78,14 @@
     <rPh sb="3" eb="4">
       <t>ビョウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>点数</t>
     <rPh sb="0" eb="2">
       <t>テンスウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>総工数(秒）</t>
@@ -114,7 +98,7 @@
     <rPh sb="4" eb="5">
       <t>ビョウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>作業準備</t>
@@ -124,14 +108,14 @@
     <rPh sb="2" eb="4">
       <t>ジュンビ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>a)単品部品総数</t>
     <rPh sb="2" eb="8">
       <t>タンピンブヒンソウスウ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>b)部品点数(1部品毎に1)</t>
@@ -141,7 +125,7 @@
     <rPh sb="8" eb="11">
       <t>ブヒンゴト</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>個装作業</t>
@@ -151,14 +135,14 @@
     <rPh sb="2" eb="4">
       <t>サギョウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>c)防錆回数</t>
     <rPh sb="2" eb="6">
       <t>ボウセイカイスウ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>d)個装数(デジタル計量部品)</t>
@@ -171,7 +155,7 @@
     <rPh sb="12" eb="14">
       <t>ブヒン</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>内装作業</t>
@@ -181,21 +165,21 @@
     <rPh sb="2" eb="4">
       <t>サギョウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>e)内装資材数</t>
     <rPh sb="2" eb="7">
       <t>ナイソウシザイスウ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>f)カートン数</t>
     <rPh sb="6" eb="7">
       <t>スウ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>f')リターナブル容器数</t>
@@ -205,14 +189,14 @@
     <rPh sb="11" eb="12">
       <t>スウ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>g)ENG発砲罪数</t>
     <rPh sb="5" eb="9">
       <t>ハッポウザイスウ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>h)積み付け回数</t>
@@ -225,7 +209,7 @@
     <rPh sb="6" eb="8">
       <t>カイスウ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>外装作業</t>
@@ -235,21 +219,21 @@
     <rPh sb="2" eb="4">
       <t>サギョウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>i)パネルケース数</t>
     <rPh sb="8" eb="9">
       <t>スウ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>j)スカシケース数</t>
     <rPh sb="8" eb="9">
       <t>スウ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>k)外装用段ボールパット使用数</t>
@@ -259,7 +243,7 @@
     <rPh sb="12" eb="15">
       <t>シヨウスウ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>l)外装用箱型ポリ袋</t>
@@ -272,7 +256,7 @@
     <rPh sb="9" eb="10">
       <t>ブクロ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>m)外装用ボルト使用数</t>
@@ -282,21 +266,21 @@
     <rPh sb="8" eb="11">
       <t>シヨウスウ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>n)外装用副資材使用数</t>
     <rPh sb="2" eb="11">
       <t>ガイソウヨウフクシザイシヨウスウ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>o)外直部品総数</t>
     <rPh sb="2" eb="8">
       <t>ガイチョクブヒンソウスウ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>p)外直の防錆回数</t>
@@ -306,7 +290,7 @@
     <rPh sb="5" eb="9">
       <t>ボウセイカイスウ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>q)外装ケース数</t>
@@ -316,7 +300,7 @@
     <rPh sb="7" eb="8">
       <t>スウ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>r)部品点数(1部品毎に1)</t>
@@ -326,21 +310,24 @@
     <rPh sb="8" eb="11">
       <t>ブヒンゴト</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>合計</t>
     <rPh sb="0" eb="2">
       <t>ゴウケイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="179" formatCode="0_);[Red]\(0\)"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -348,14 +335,6 @@
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="游ゴシック Light"/>
-      <family val="2"/>
-      <charset val="128"/>
-      <scheme val="major"/>
     </font>
     <font>
       <sz val="10"/>
@@ -598,89 +577,89 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -701,142 +680,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>317500</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>645272</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>115038</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="テキスト ボックス 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5956303-473D-474E-A542-5E523288803C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1003300" y="0"/>
-          <a:ext cx="327772" cy="296013"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>①</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>107950</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>435722</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>38838</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="テキスト ボックス 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC1194C0-7863-4163-AB63-3AA3E46EC093}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="793750" y="276225"/>
-          <a:ext cx="327772" cy="305538"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>②</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
@@ -1269,7 +1112,7 @@
     <tabColor theme="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:F32"/>
+  <dimension ref="B3:F32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1279,36 +1122,28 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B4" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2"/>
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B5" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" s="2"/>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B6" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" s="2"/>
       <c r="F6" s="2"/>
@@ -1322,311 +1157,296 @@
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="F8" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="7">
-        <f>ROUND(D9*E9,0)</f>
-        <v>0</v>
-      </c>
+      <c r="D9" s="21"/>
+      <c r="E9" s="8" t="e">
+        <f>F9/D9</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F9" s="21"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B10" s="9"/>
       <c r="C10" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11">
-        <f>ROUND(D10*E10,0)</f>
-        <v>0</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="D10" s="22"/>
+      <c r="E10" s="8" t="e">
+        <f t="shared" ref="E10:E30" si="0">F10/D10</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F10" s="22"/>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B11" s="12"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="11">
-        <f>SUM(F9:F10)</f>
-        <v>0</v>
-      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="22"/>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="7">
-        <f>ROUND(D12*E12,0)</f>
-        <v>0</v>
-      </c>
+      <c r="D12" s="21"/>
+      <c r="E12" s="8" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F12" s="21"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B13" s="9"/>
       <c r="C13" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="10">
-        <f>ROUND(D13*E13,0)</f>
-        <v>0</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="D13" s="22"/>
+      <c r="E13" s="8" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F13" s="22"/>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B14" s="12"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="10">
-        <f>SUM(F12:F13)</f>
-        <v>0</v>
-      </c>
+      <c r="B14" s="11"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="22"/>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="18">
-        <f>ROUND(D15*E15,0)</f>
-        <v>0</v>
-      </c>
+      <c r="D15" s="25"/>
+      <c r="E15" s="8" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F15" s="25"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B16" s="9"/>
-      <c r="C16" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="18">
-        <f>ROUND(D16*E16,0)</f>
-        <v>0</v>
-      </c>
+      <c r="C16" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="25"/>
+      <c r="E16" s="8" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F16" s="25"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B17" s="9"/>
-      <c r="C17" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="18">
-        <f>ROUND(D17*E17,0)</f>
-        <v>0</v>
-      </c>
+      <c r="C17" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="25"/>
+      <c r="E17" s="8" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F17" s="25"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B18" s="9"/>
-      <c r="C18" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="18">
-        <f>ROUND(D18*E18,0)</f>
-        <v>0</v>
-      </c>
+      <c r="C18" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="25"/>
+      <c r="E18" s="8" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F18" s="25"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B19" s="9"/>
       <c r="C19" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="10">
-        <f>ROUND(D19*E19,0)</f>
-        <v>0</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="D19" s="22"/>
+      <c r="E19" s="8" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F19" s="22"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B20" s="12"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="10">
-        <f>SUM(F15:F19)</f>
-        <v>0</v>
-      </c>
+      <c r="B20" s="11"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="22"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B21" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="7">
-        <f t="shared" ref="F21:F30" si="0">ROUND(D21*E21,0)</f>
-        <v>0</v>
-      </c>
+      <c r="D21" s="21"/>
+      <c r="E21" s="8" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F21" s="21"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B22" s="9"/>
-      <c r="C22" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="C22" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="25"/>
+      <c r="E22" s="8" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F22" s="25"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B23" s="9"/>
-      <c r="C23" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="C23" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" s="25"/>
+      <c r="E23" s="8" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F23" s="25"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B24" s="9"/>
-      <c r="C24" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="C24" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="25"/>
+      <c r="E24" s="8" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F24" s="25"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B25" s="9"/>
-      <c r="C25" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="C25" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="25"/>
+      <c r="E25" s="8" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F25" s="25"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B26" s="9"/>
-      <c r="C26" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="C26" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="25"/>
+      <c r="E26" s="8" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F26" s="25"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B27" s="9"/>
-      <c r="C27" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="C27" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="25"/>
+      <c r="E27" s="8" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F27" s="25"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B28" s="9"/>
-      <c r="C28" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="C28" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" s="25"/>
+      <c r="E28" s="8" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F28" s="25"/>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B29" s="9"/>
-      <c r="C29" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="C29" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" s="26"/>
+      <c r="E29" s="8" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F29" s="25"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B30" s="9"/>
-      <c r="C30" s="22" t="s">
+      <c r="C30" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" s="27"/>
+      <c r="E30" s="8" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F30" s="27"/>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B31" s="11"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="28"/>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B32" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B31" s="12"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="25">
-        <f>SUM(F21:F30)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B32" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="25">
-        <f>SUM(F31,F20,F14,F11)</f>
-        <v>0</v>
-      </c>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="28"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="24" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>

--- a/Honda_Logi/Excel_Format/モジュール別包装費明細.xlsx
+++ b/Honda_Logi/Excel_Format/モジュール別包装費明細.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01_hida_data\78_Honda_ロジ\01_PG\git\Honda_Logi\Excel_Format\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8338A95D-AB61-4E97-86D2-366871959320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C6D6BF4-053B-47C7-9CFF-C33993D269BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{8DDBEA3C-F131-4B47-9603-2E5186CE90A5}"/>
+    <workbookView xWindow="28680" yWindow="1965" windowWidth="25440" windowHeight="15390" xr2:uid="{8DDBEA3C-F131-4B47-9603-2E5186CE90A5}"/>
   </bookViews>
   <sheets>
     <sheet name="モジュール別包装費明細" sheetId="1" r:id="rId1"/>
@@ -324,10 +324,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="179" formatCode="0_);[Red]\(0\)"/>
-  </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -357,6 +354,14 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -568,12 +573,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -598,9 +606,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -637,32 +642,33 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="桁区切り" xfId="1" builtinId="6"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1179,31 +1185,31 @@
       <c r="C9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="21"/>
-      <c r="E9" s="8" t="e">
+      <c r="D9" s="20"/>
+      <c r="E9" s="20" t="e">
         <f>F9/D9</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F9" s="21"/>
+      <c r="F9" s="20"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B10" s="9"/>
-      <c r="C10" s="10" t="s">
+      <c r="B10" s="8"/>
+      <c r="C10" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="8" t="e">
+      <c r="D10" s="21"/>
+      <c r="E10" s="20" t="e">
         <f t="shared" ref="E10:E30" si="0">F10/D10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F10" s="22"/>
+      <c r="F10" s="21"/>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B11" s="11"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="22"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="21"/>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B12" s="6" t="s">
@@ -1212,100 +1218,100 @@
       <c r="C12" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="21"/>
-      <c r="E12" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F12" s="21"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F12" s="20"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B13" s="9"/>
-      <c r="C13" s="10" t="s">
+      <c r="B13" s="8"/>
+      <c r="C13" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="22"/>
-      <c r="E13" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F13" s="22"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="20" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F13" s="21"/>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B14" s="11"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="22"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="21"/>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="25"/>
-      <c r="E15" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F15" s="25"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="20" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F15" s="22"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B16" s="9"/>
-      <c r="C16" s="14" t="s">
+      <c r="B16" s="8"/>
+      <c r="C16" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="25"/>
-      <c r="E16" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F16" s="25"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="20" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F16" s="22"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B17" s="9"/>
-      <c r="C17" s="14" t="s">
+      <c r="B17" s="8"/>
+      <c r="C17" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="25"/>
-      <c r="E17" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F17" s="25"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="20" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F17" s="22"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B18" s="9"/>
-      <c r="C18" s="14" t="s">
+      <c r="B18" s="8"/>
+      <c r="C18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="25"/>
-      <c r="E18" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F18" s="25"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="20" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F18" s="22"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B19" s="9"/>
-      <c r="C19" s="10" t="s">
+      <c r="B19" s="8"/>
+      <c r="C19" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="22"/>
-      <c r="E19" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F19" s="22"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="20" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F19" s="21"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B20" s="11"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="22"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="21"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B21" s="6" t="s">
@@ -1314,136 +1320,136 @@
       <c r="C21" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="21"/>
-      <c r="E21" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F21" s="21"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F21" s="20"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B22" s="9"/>
-      <c r="C22" s="14" t="s">
+      <c r="B22" s="8"/>
+      <c r="C22" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="25"/>
-      <c r="E22" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F22" s="25"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="20" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F22" s="22"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B23" s="9"/>
-      <c r="C23" s="14" t="s">
+      <c r="B23" s="8"/>
+      <c r="C23" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="25"/>
-      <c r="E23" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F23" s="25"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="20" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F23" s="22"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B24" s="9"/>
-      <c r="C24" s="14" t="s">
+      <c r="B24" s="8"/>
+      <c r="C24" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="25"/>
-      <c r="E24" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F24" s="25"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="20" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F24" s="22"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B25" s="9"/>
-      <c r="C25" s="14" t="s">
+      <c r="B25" s="8"/>
+      <c r="C25" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="25"/>
-      <c r="E25" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F25" s="25"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="20" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F25" s="22"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B26" s="9"/>
-      <c r="C26" s="14" t="s">
+      <c r="B26" s="8"/>
+      <c r="C26" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D26" s="25"/>
-      <c r="E26" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F26" s="25"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="20" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F26" s="22"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B27" s="9"/>
-      <c r="C27" s="14" t="s">
+      <c r="B27" s="8"/>
+      <c r="C27" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D27" s="25"/>
-      <c r="E27" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F27" s="25"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="20" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F27" s="22"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B28" s="9"/>
-      <c r="C28" s="14" t="s">
+      <c r="B28" s="8"/>
+      <c r="C28" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="25"/>
-      <c r="E28" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F28" s="25"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="20" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F28" s="22"/>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B29" s="9"/>
-      <c r="C29" s="15" t="s">
+      <c r="B29" s="8"/>
+      <c r="C29" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D29" s="26"/>
-      <c r="E29" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F29" s="25"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="20" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F29" s="22"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B30" s="9"/>
-      <c r="C30" s="16" t="s">
+      <c r="B30" s="8"/>
+      <c r="C30" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="27"/>
-      <c r="E30" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F30" s="27"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="20" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F30" s="23"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B31" s="11"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="28"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="24"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="28"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="24"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
